--- a/Data/Submission_Final.xlsx
+++ b/Data/Submission_Final.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://ada.edu.au/</t>
+          <t>https://zenodo.org/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=qdpx</t>
+          <t>https://zenodo.org/search?q=qdpx</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -553,15 +553,19 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14 20:21:28</t>
+          <t>2026-03-28 22:20:42</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>zenodo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -585,16 +589,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://ada.edu.au/</t>
+          <t>https://zenodo.org/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=mqda</t>
+          <t>https://zenodo.org/search?q=mqda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -614,16 +618,24 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>cc0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14 20:21:29</t>
+          <t>2026-03-28 22:20:43</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>zenodo</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -647,16 +659,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://ada.edu.au/</t>
+          <t>https://zenodo.org/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=interview study</t>
+          <t>https://zenodo.org/search?q=interview+study</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -677,15 +689,19 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14 20:21:30</t>
+          <t>2026-03-28 22:20:43</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>zenodo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -709,16 +725,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/</t>
+          <t>https://dataverse.no/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/simple-search?query=qdpx</t>
+          <t>https://dataverse.no/dataverse/root/?q=qdpx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -743,19 +759,15 @@
           <t>mit</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2019-12-18</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14 20:21:30</t>
+          <t>2026-03-28 22:20:43</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>uni-halle</t>
+          <t>dataverse-no</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -779,16 +791,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/</t>
+          <t>https://dataverse.no/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/simple-search?query=mqda</t>
+          <t>https://dataverse.no/dataverse/root/?q=mqda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -813,19 +825,15 @@
           <t>mit</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2019-12-18</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14 20:21:30</t>
+          <t>2026-03-28 22:20:43</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>uni-halle</t>
+          <t>dataverse-no</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -849,16 +857,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/</t>
+          <t>https://dataverse.no/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://opendata.uni-halle.de/simple-search?query=interview study</t>
+          <t>https://dataverse.no/dataverse/root/?q=interview+study</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -883,27 +891,419 @@
           <t>mit</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:44</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dataverse-no</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>folder_interview study</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>qdpx</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://ada.edu.au/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=qdpx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Project qdpx</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:45</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ada</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>folder_qdpx</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mqda</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://ada.edu.au/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=mqda</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Project mqda</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:46</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ada</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>folder_mqda</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>interview study</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://ada.edu.au/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://dataverse.ada.edu.au/dataverse/ada/?q=interview+study</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Project interview study</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:47</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ada</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>folder_interview study</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>qdpx</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/simple-search?query=qdpx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Project qdpx</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mit</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>2019-12-18</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-03-14 20:21:30</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:47</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>uni-halle</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>folder_qdpx</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mqda</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/simple-search?query=mqda</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Project mqda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>mit</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2019-12-18</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:48</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>uni-halle</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>folder_mqda</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SCRAPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>interview study</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://opendata.uni-halle.de/simple-search?query=interview+study</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Project interview study</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Phase 1: Metadata Extraction</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mit</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2019-12-18</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:48</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>uni-halle</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>folder_interview study</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>SCRAPING</t>
         </is>
@@ -956,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1449,84 @@
         <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>interview study</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>qdpx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mqda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>interview study</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>qdpx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mqda</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>interview study</t>
         </is>
